--- a/diseases/d011/1995-1999.xlsx
+++ b/diseases/d011/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10735,9 +10660,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11128,9 +11050,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11666,9 +11585,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12204,9 +12120,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12742,9 +12655,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13280,9 +13190,6 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13818,9 +13725,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14356,9 +14260,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14894,9 +14795,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15432,9 +15330,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="S79" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15970,9 +15865,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16508,9 +16400,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="S85" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17046,9 +16935,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17584,9 +17470,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="S91" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17977,9 +17860,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="S93" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18515,9 +18395,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19053,9 +18930,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19591,9 +19465,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20129,9 +20000,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20667,9 +20535,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21205,9 +21070,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21743,9 +21605,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22281,9 +22140,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22819,9 +22675,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23357,9 +23210,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23895,9 +23745,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24433,9 +24280,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24826,9 +24670,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25364,9 +25205,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25902,9 +25740,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26440,9 +26275,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26978,9 +26810,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27516,9 +27345,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28054,9 +27880,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28592,9 +28415,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29130,9 +28950,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29668,9 +29485,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30205,9 +30019,6 @@
       </c>
       <c r="O161" t="n">
         <v>1</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
